--- a/docs/downloads/top_results.xlsx
+++ b/docs/downloads/top_results.xlsx
@@ -9,13 +9,13 @@
     <sheet name="Top results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Top results'!$A$1:$M$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Top results'!$A$1:$M$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t xml:space="preserve">agency</t>
   </si>
@@ -59,6 +59,27 @@
     <t xml:space="preserve">DHHS</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) Service Area Competition (SAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-HRSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forecasted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $22.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.25 FTE fits your staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/c30fddfd-2094-4cf0-ba21-04b6736fc755</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0009</t>
   </si>
   <si>
@@ -68,10 +89,7 @@
     <t xml:space="preserve">HHS-CDC-NCHHSTP</t>
   </si>
   <si>
-    <t xml:space="preserve">forecasted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 70 days to deadline · ~$7.5M implied award · no cost share → Tier 1: writer can act</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 139 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.5 FTE fits your staff</t>
@@ -89,37 +107,256 @@
     <t xml:space="preserve">HHS-CDC-NCEZID</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 96 days to deadline · ~$110.0M implied award · no cost share → Tier 1: writer can act</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 96 days to deadline · up to $22.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/38e79010-c2a9-4d5f-bf81-cede591318e4</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 Service Area Competition (SAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $19.2M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/51fa7e21-beca-497f-a0f1-bf175382f77f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 100 days to deadline · up to $15.3M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6076b54f-ab56-4ed2-81f5-8b43c030a4c0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan White HIV/AIDS Program Part B States/Territories Supplemental Grant Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 166 days to deadline · up to $9.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/be465a8b-8694-4eef-9801-5160a92c7cdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIDS Drug Assistance Program (ADAP) Emergency Relief Funds (ERF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 33 days to deadline · up to $10.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1613e128-508f-47e1-9bf2-e2c02e7d79b1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetal, Infant, and Child Death Review Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 112 days to deadline · up to $5.1M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/d9551b09-3a45-4dc1-a343-3f09521de9aa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-IP-27-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expanded Surveillance for Pediatric Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-HHSCDCERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · up to $1.1M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b3577f33-eee0-49fb-aeba-2ea0b02fe59e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year 2027 Regional Nutrition Hubs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 62 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/8b2aa3e2-733a-44d8-876e-56df42678c9a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The National Network of STI Prevention Training Centers (NNPTC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 143 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/217a3975-7543-445d-9638-8026297a75c4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Maternity and Obstetrics Management Strategies Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 202 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/741f2935-18c1-4e3e-8f54-f30dc3a6ee80</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0008</t>
   </si>
   <si>
     <t xml:space="preserve">Controlling and Preventing STIs in US Health Departments (CAP-STIs)</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 31 days to deadline · ~$8.5M implied award · no cost share → Tier 1: writer can act</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 103 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
   </si>
   <si>
-    <t xml:space="preserve">RFA-IP-27-035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expanded Surveillance for Pediatric Infectious Diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-HHSCDCERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · ~$5.7M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b3577f33-eee0-49fb-aeba-2ea0b02fe59e</t>
+    <t xml:space="preserve">HRSA-27-046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Residency Planning and Development Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 169 days to deadline · up to $750K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6bc69d9c-87b7-4329-962c-16c8e3ad553d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 182 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 208 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 243 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR-FD-23-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-FDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · no deadline stated · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-DP-27-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation Research on Coordinated Combinations of Community-Clinical Linkage Strategies for Diabetes Prevention and Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 173 days to deadline · up to $725K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/54666d94-e0dc-44d3-90e6-6eb913f79ca9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 110 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-OH-27-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State Occupational Safety and Health Surveillance Program (U60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $685K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/13af439f-7405-4592-9a1e-18c4f7db7622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Health Value Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 171 days to deadline · up to $650K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/33b8d341-8908-46c1-95c1-a8af9be3ccc8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Health Network Development Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 167 days to deadline · up to $500K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/8bb15754-c013-462d-b305-f2a8dd116e08</t>
   </si>
   <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0239</t>
@@ -128,22 +365,34 @@
     <t xml:space="preserve">Strengthening Services to Prevent the Infectious Disease Consequences of Drug Use</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 236 days to deadline · ~$41.2M implied award · no cost share → Tier 1: writer can act</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 236 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The National Network of STI Prevention Training Centers (NNPTC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 143 days to deadline · ~$4.0M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/217a3975-7543-445d-9638-8026297a75c4</t>
+    <t xml:space="preserve">HRSA-27-039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiation Exposure Screening and Education Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 237 days to deadline · up to $500K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/188aac01-0056-4dd0-9bde-54cf6ddf113c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telehealth Nutrition Services Network Grant Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 213 days to deadline · up to $300K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/18c0a9f1-fe39-4c7a-8ffd-1d8c656d666f</t>
   </si>
   <si>
     <t xml:space="preserve">HRSA-27-063</t>
@@ -152,216 +401,12 @@
     <t xml:space="preserve">HIV Care Grant Program - Part B States/Territories Formula and AIDS Drug Assistance Program Formula and AIDS Drug Assistance Program Supplemental Awards</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-HRSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 30 days to deadline · ~$24.8M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.25 FTE fits your staff</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/1d55627c-531e-4a60-95e0-719b256179bf</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 243 days to deadline · ~$3.0M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetal, Infant, and Child Death Review Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 112 days to deadline · ~$5.1M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/d9551b09-3a45-4dc1-a343-3f09521de9aa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 182 days to deadline · ~$2.8M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-DP-27-051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementation Research on Coordinated Combinations of Community-Clinical Linkage Strategies for Diabetes Prevention and Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 173 days to deadline · ~$2.5M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/54666d94-e0dc-44d3-90e6-6eb913f79ca9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 208 days to deadline · ~$2.2M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-OH-27-050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State Occupational Safety and Health Surveillance Program (U60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · ~$1.6M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/13af439f-7405-4592-9a1e-18c4f7db7622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan White HIV/AIDS Program Part B States/Territories Supplemental Grant Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 166 days to deadline · ~$1.6M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/be465a8b-8694-4eef-9801-5160a92c7cdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIDS Drug Assistance Program (ADAP) Emergency Relief Funds (ERF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 33 days to deadline · ~$2.5M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1613e128-508f-47e1-9bf2-e2c02e7d79b1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR-FD-23-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-FDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · no deadline stated · award size not stated · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Maternity and Obstetrics Management Strategies Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 202 days to deadline · ~$1.0M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/741f2935-18c1-4e3e-8f54-f30dc3a6ee80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Residency Planning and Development Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 169 days to deadline · ~$750K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6bc69d9c-87b7-4329-962c-16c8e3ad553d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 110 days to deadline · ~$700K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Health Value Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 171 days to deadline · ~$650K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/33b8d341-8908-46c1-95c1-a8af9be3ccc8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radiation Exposure Screening and Education Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 237 days to deadline · ~$486K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/188aac01-0056-4dd0-9bde-54cf6ddf113c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Health Network Development Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 167 days to deadline · ~$391K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/8bb15754-c013-462d-b305-f2a8dd116e08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telehealth Nutrition Services Network Grant Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 213 days to deadline · ~$300K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/18c0a9f1-fe39-4c7a-8ffd-1d8c656d666f</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDC-RFA-TP22-2201</t>
   </si>
   <si>
@@ -374,7 +419,7 @@
     <t xml:space="preserve">posted</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · partner needed for emergency management · 134 days to deadline · ~$4.4M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply · partner needed for emergency management · 134 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">Needs emergency management, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
@@ -383,21 +428,99 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/42a1b238-2c19-47b4-ae58-f4a775231b78</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-DP-27-0072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promoting Population Health through Increased Capacity in Alcohol Epidemiology &amp; the Prevention of Excessive Alcohol Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 212 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6d44bb23-2a1f-4e12-8d72-c2b5b46195d4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-ACF-ORR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 366 days to deadline · up to $100.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-CK-26-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $6.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
+  </si>
+  <si>
     <t xml:space="preserve">RFA-OH-24-001</t>
   </si>
   <si>
     <t xml:space="preserve">National Center for Construction Safety and Health Research and Translation (U54)</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · partner needed for research and rigorous evaluation · 62 days to deadline · ~$28.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner</t>
+    <t xml:space="preserve">state agency can apply · partner needed for research and rigorous evaluation · 62 days to deadline · up to $5.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/b307f2ac-767d-4715-be92-f5326db2cd9d</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Communities Opioid Response Program - Community Systems Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 188 days to deadline · up to $500K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires funding and monitoring subrecipients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/02b2d236-f596-4aca-874d-b8e364156ddc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing; partner needed for emergency management · 117 days to deadline · up to $4.9M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Needs emergency management, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-CE-27-0024</t>
   </si>
   <si>
@@ -407,7 +530,7 @@
     <t xml:space="preserve">HHS-CDC-NCIPC</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 199 days to deadline · ~$4.5M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 199 days to deadline · up to $1.2M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
@@ -416,19 +539,46 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/3c36bc50-73ae-42ad-a727-fae640dad5c9</t>
   </si>
   <si>
-    <t xml:space="preserve">RFA-CK-26-035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · ~$15.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
+    <t xml:space="preserve">HRSA-27-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $6.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 174 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 146 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-OH-27-049</t>
@@ -437,22 +587,31 @@
     <t xml:space="preserve">NIOSH Centers of Excellence for Total Worker Health® (U19)</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 149 days to deadline · ~$5.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 149 days to deadline · up to $1.4M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/43e32c6d-fbbd-4056-8fd4-f64cdebefd41</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
+  </si>
+  <si>
     <t xml:space="preserve">RFA-CK-26-036</t>
   </si>
   <si>
     <t xml:space="preserve">US Travelers Health Research, Surveillance, Communication, and Outreach Network</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · ~$5.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">Cooperative agreement with a required evaluation</t>
@@ -461,166 +620,106 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/1a3231f6-36eb-40d1-afe8-232010fa2fe3</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health Workforce Research Center (HWRC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 160 days to deadline · up to $900K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/9accc70c-9683-4b78-bb7b-e8fdbcff1b47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 159 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-DP-27-036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 174 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 244 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-DHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 488 days to deadline · award not stated on Grants.gov · cost share required (25% stated) → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share required (25% stated): supervisor must approve match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-DP-27-0043</t>
   </si>
   <si>
     <t xml:space="preserve">Statewide Perinatal Quality Collaboratives: Improving Perinatal Care and Outcomes</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 215 days to deadline · ~$2.1M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 215 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-ACF-ORR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 366 days to deadline · ~$27.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-DP-27-036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 174 days to deadline · ~$3.6M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 174 days to deadline · ~$5.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · ~$6.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DP-27-0072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promoting Population Health through Increased Capacity in Alcohol Epidemiology &amp; the Prevention of Excessive Alcohol Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 212 days to deadline · ~$1.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6d44bb23-2a1f-4e12-8d72-c2b5b46195d4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 146 days to deadline · ~$5.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Communities Opioid Response Program - Community Systems Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 188 days to deadline · ~$500K implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires funding and monitoring subrecipients</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/02b2d236-f596-4aca-874d-b8e364156ddc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 244 days to deadline · ~$2.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · ~$700K implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing; partner needed for emergency management · 117 days to deadline · ~$1.5M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Needs emergency management, which DHHS reaches only through a partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 159 days to deadline · ~$1.4M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
+    <t xml:space="preserve">RFA-OH-25-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupational Safety and Health Training Project Grants (T03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 757 days to deadline · up to $550K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0731381f-f39a-4d8f-9f55-701eddc5273b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-CE-27-0052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preventing Violence Affecting Young Lives (PREVAYL 2.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 215 days to deadline · up to $450K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f2ea8925-6244-47e8-8de5-ffe0007096e7</t>
   </si>
   <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0061</t>
@@ -629,54 +728,12 @@
     <t xml:space="preserve">Demonstration Projects for Whole-Person Health Models for Women Living with HIV in the South</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 166 days to deadline · ~$2.5M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 166 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/06024144-a58a-42d8-8813-75357d9bb7fe</t>
   </si>
   <si>
-    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHS-DHS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 488 days to deadline · award size not stated · cost share required (25% stated) → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share required (25% stated): supervisor must approve match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-OH-25-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupational Safety and Health Training Project Grants (T03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 757 days to deadline · ~$828K implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0731381f-f39a-4d8f-9f55-701eddc5273b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health Workforce Research Center (HWRC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 160 days to deadline · ~$450K implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/9accc70c-9683-4b78-bb7b-e8fdbcff1b47</t>
-  </si>
-  <si>
     <t xml:space="preserve">VA-GPD-FORECAST-FY2026-FY2028</t>
   </si>
   <si>
@@ -686,7 +743,7 @@
     <t xml:space="preserve">VA-HPGPDP</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for housing stock or assistance · no deadline stated · award size not stated · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for housing stock or assistance · no deadline stated · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">Needs housing stock or assistance, which DHHS reaches only through a partner</t>
@@ -704,10 +761,10 @@
     <t xml:space="preserve">HHS-ACF</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 48 days to deadline · ~$9.0M implied award · cost share required (30% stated) → Tier 3: needs secretary or legislature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share on a ~$9.0M award likely needs a state appropriation (line set at $1.0M); Requires a formal state designation (e.g. by the Governor); Cost share required (30% stated): supervisor must approve match</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 51 days to deadline · up to $15.0M (Grants.gov ceiling) · cost share required (30% stated) → Tier 3: needs secretary or legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share on a ~$15M award likely needs a state appropriation (line set at $1.0M); Requires a formal state designation (e.g. by the Governor); Cost share required (30% stated): supervisor must approve match</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8d272419-96d1-4898-9706-0d86a1e63c03</t>
@@ -719,10 +776,10 @@
     <t xml:space="preserve">Maternal, Infant, and Early Childhood Home Visiting Program (MIECHV)</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 169 days to deadline · ~$11.6M implied award · cost share required (percentage not published) → Tier 3: needs secretary or legislature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share on a ~$12M award likely needs a state appropriation (line set at $1.0M); Needs workforce training and credentialing, which DHHS reaches only through a partner; Cost share required (percentage not published): supervisor must approve match</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 169 days to deadline · up to $48.6M (Grants.gov ceiling) · cost share required (percentage not published) → Tier 3: needs secretary or legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share on a ~$49M award likely needs a state appropriation (line set at $1.0M); Needs workforce training and credentialing, which DHHS reaches only through a partner; Cost share required (percentage not published): supervisor must approve match</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/f68cf378-43e2-49b9-a252-a7009c6b81cf</t>
@@ -737,10 +794,10 @@
     <t xml:space="preserve">HHS-OPHS</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 103 days to deadline · ~$2.9M implied award · cost share required (percentage not published) → Tier 3: needs secretary or legislature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share on a ~$2.9M award likely needs a state appropriation (line set at $1.0M); Cost share required (percentage not published): supervisor must approve match; Requires funding and monitoring subrecipients</t>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 103 days to deadline · up to $22.0M (Grants.gov ceiling) · cost share required (percentage not published) → Tier 3: needs secretary or legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share on a ~$22M award likely needs a state appropriation (line set at $1.0M); Cost share required (percentage not published): supervisor must approve match; Requires funding and monitoring subrecipients</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/770eae58-b245-4431-a4b8-7b1aca9e917f</t>
@@ -758,7 +815,7 @@
     <t xml:space="preserve">VA-CSHF</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · partner needed for capital construction · no deadline stated · ~$275.0M ceiling · cost share required (35% stated) → Tier 3: needs secretary or legislature</t>
+    <t xml:space="preserve">state agency can apply · partner needed for capital construction · no deadline stated · up to $275.0M (Grants.gov ceiling) · cost share required (35% stated) → Tier 3: needs secretary or legislature</t>
   </si>
   <si>
     <t xml:space="preserve">Cost share on a ~$275M award likely needs a state appropriation (line set at $1.0M); Capital construction project; Requires a formal state designation (e.g. by the Governor); Needs capital construction, which DMVA reaches only through a partner; Cost share required (35% stated): supervisor must approve match</t>
@@ -767,10 +824,28 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/59462b36-6d05-4832-a628-427f72260f3d</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · no route to behavioral health service delivery; partner needed for housing stock or assistance · no deadline stated · award size not stated · no cost share → Tier 3: needs secretary or legislature</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · no route to behavioral health service delivery; partner needed for housing stock or assistance · no deadline stated · award not stated on Grants.gov · no cost share → Tier 3: needs secretary or legislature</t>
   </si>
   <si>
     <t xml:space="preserve">Needs behavioral health service delivery, which DMVA has no route to; Needs housing stock or assistance, which DMVA reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA-NCA-VLGP-FY2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veterans Legacy Grants Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA-VLGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · no route to public health surveillance · 191 days to deadline · up to $400K (Grants.gov ceiling) · no cost share → Tier 3: needs secretary or legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs public health surveillance, which DMVA has no route to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/8d1358e4-662b-4359-aa77-e553a65a6511</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>14</v>
@@ -1204,10 +1279,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>46365</v>
+        <v>46386</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>7500000</v>
+        <v>22024900</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>18</v>
@@ -1230,7 +1305,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>21</v>
@@ -1245,19 +1320,17 @@
         <v>17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46391</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>110000000</v>
-      </c>
+        <v>46434</v>
+      </c>
+      <c r="J3" s="3"/>
       <c r="K3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -1271,34 +1344,34 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>46326</v>
+        <v>46391</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>8474576.27118644</v>
+        <v>22000000</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -1312,34 +1385,34 @@
         <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>46387</v>
+        <v>46386</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>5714285.71428571</v>
+        <v>19182000</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -1353,13 +1426,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>16</v>
@@ -1368,10 +1441,10 @@
         <v>17</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>46531</v>
+        <v>46395</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>41250000</v>
+        <v>15335500</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>37</v>
@@ -1394,7 +1467,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>39</v>
@@ -1409,10 +1482,10 @@
         <v>17</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>46438</v>
+        <v>46461</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4000000</v>
+        <v>9000000</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>41</v>
@@ -1444,25 +1517,25 @@
         <v>44</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>46328</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>46325</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>24809259.2592593</v>
-      </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1479,10 +1552,10 @@
         <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>16</v>
@@ -1491,19 +1564,19 @@
         <v>17</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>46538</v>
+        <v>46407</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>3000000</v>
+        <v>5149000</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1517,34 +1590,34 @@
         <v>9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>46387</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>46407</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>5149000</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -1558,34 +1631,34 @@
         <v>10</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>46357</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="L11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>46477</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>2750000</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -1599,34 +1672,34 @@
         <v>11</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>46438</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="L12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>46468</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -1640,34 +1713,34 @@
         <v>12</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>46497</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="L13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>46503</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2217391.30434783</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1681,34 +1754,32 @@
         <v>13</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>46398</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="L14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>46386</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="15">
@@ -1722,34 +1793,34 @@
         <v>14</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>46464</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>750000</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="L15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>46461</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -1763,34 +1834,32 @@
         <v>15</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>46477</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>46328</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="K16" s="3" t="s">
+      <c r="L16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="17">
@@ -1804,30 +1873,32 @@
         <v>16</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="G17" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="3"/>
+      <c r="I17" s="3" t="n">
+        <v>46503</v>
+      </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -1841,34 +1912,32 @@
         <v>17</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>46538</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="L18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>46497</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -1882,34 +1951,30 @@
         <v>18</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>46464</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>750000</v>
-      </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="20">
@@ -1923,34 +1988,34 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>46468</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>725000</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>46405</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>700000</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="21">
@@ -1964,34 +2029,34 @@
         <v>20</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>46405</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>46466</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>650000</v>
-      </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="22">
@@ -2005,34 +2070,34 @@
         <v>21</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>46386</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>685000</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>46532</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>486125</v>
-      </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="23">
@@ -2046,34 +2111,34 @@
         <v>22</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>46466</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>650000</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>46462</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>391304.347826087</v>
-      </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="24">
@@ -2087,34 +2152,34 @@
         <v>23</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>46462</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>46508</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>300000</v>
-      </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="25">
@@ -2122,40 +2187,38 @@
         <v>13</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>46531</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="L25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>46429</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>4424778.76106195</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="26">
@@ -2163,40 +2226,40 @@
         <v>13</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46357</v>
+        <v>46532</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>28750000</v>
+        <v>500000</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
@@ -2204,40 +2267,40 @@
         <v>13</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46494</v>
+        <v>46508</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>4519230.76923077</v>
+        <v>300000</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28">
@@ -2245,40 +2308,38 @@
         <v>13</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>15000000</v>
-      </c>
+        <v>46387</v>
+      </c>
+      <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29">
@@ -2289,37 +2350,37 @@
         <v>2</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>46444</v>
+        <v>46429</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5850000</v>
+        <v>5000000</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30">
@@ -2330,37 +2391,35 @@
         <v>2</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>5000000</v>
-      </c>
+        <v>46507</v>
+      </c>
+      <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
@@ -2371,37 +2430,37 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>61</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>46661</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>46510</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>2141025.64102564</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="32">
@@ -2412,37 +2471,37 @@
         <v>2</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>60</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>46331</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>46661</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>27750000</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="33">
@@ -2453,37 +2512,37 @@
         <v>2</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>46469</v>
+        <v>46357</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>3625000</v>
+        <v>5750000</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34">
@@ -2494,37 +2553,37 @@
         <v>2</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>46469</v>
+        <v>46483</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35">
@@ -2535,37 +2594,37 @@
         <v>2</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>58</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>46412</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M35" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>46498</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>6750000</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="36">
@@ -2576,37 +2635,37 @@
         <v>2</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>58</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>46494</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="M36" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>46507</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>1002916.66666667</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="37">
@@ -2617,37 +2676,37 @@
         <v>2</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>46498</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>46441</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="K37" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="38">
@@ -2658,37 +2717,37 @@
         <v>2</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>46483</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>500000</v>
-      </c>
-      <c r="K38" s="3" t="s">
+      <c r="L38" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="L38" s="3" t="s">
+      <c r="M38" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="39">
@@ -2699,16 +2758,16 @@
         <v>2</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>56</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>16</v>
@@ -2717,19 +2776,19 @@
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>46539</v>
+        <v>46441</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>2750000</v>
+        <v>5000000</v>
       </c>
       <c r="K39" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="40">
@@ -2740,37 +2799,37 @@
         <v>2</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>46444</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>46498</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>700000</v>
-      </c>
-      <c r="K40" s="3" t="s">
+      <c r="L40" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="M40" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="41">
@@ -2781,37 +2840,37 @@
         <v>2</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>46498</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>46412</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>1461538.46153846</v>
-      </c>
-      <c r="K41" s="3" t="s">
+      <c r="L41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M41" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="42">
@@ -2822,37 +2881,37 @@
         <v>2</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>46331</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="L42" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>46454</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>1423076.92307692</v>
-      </c>
-      <c r="K42" s="3" t="s">
+      <c r="M42" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="43">
@@ -2863,16 +2922,16 @@
         <v>2</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>50</v>
       </c>
       <c r="E43" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>16</v>
@@ -2881,19 +2940,19 @@
         <v>17</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>46461</v>
+        <v>46455</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>2500000</v>
+        <v>900000</v>
       </c>
       <c r="K43" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="44">
@@ -2904,35 +2963,35 @@
         <v>2</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="G44" s="3" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>46783</v>
+        <v>46454</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45">
@@ -2943,37 +3002,35 @@
         <v>2</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>47052</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>827586.206896552</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="46">
@@ -2984,37 +3041,35 @@
         <v>2</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>46539</v>
+      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>46455</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>450000</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="47">
@@ -3025,33 +3080,35 @@
         <v>2</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>46783</v>
+      </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48">
@@ -3059,40 +3116,38 @@
         <v>13</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>46510</v>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>46343</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>8960000</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="49">
@@ -3100,40 +3155,40 @@
         <v>13</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46464</v>
+        <v>47052</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>11614285.7142857</v>
+        <v>550000</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50">
@@ -3141,102 +3196,102 @@
         <v>13</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>239</v>
+        <v>170</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>46398</v>
+        <v>46510</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2855555.55555556</v>
+        <v>450000</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>243</v>
+        <v>13</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>246</v>
+        <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3" t="n">
-        <v>275000000</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>46461</v>
+      </c>
+      <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>248</v>
+        <v>172</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>243</v>
+        <v>13</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>17</v>
@@ -3244,17 +3299,257 @@
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>46346</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="M53" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="L52" s="3" t="s">
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>225</v>
+      <c r="F54" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>46464</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>48596938</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>46398</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3" t="n">
+        <v>275000000</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>46486</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M52"/>
+  <autoFilter ref="A1:M58"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/docs/downloads/top_results.xlsx
+++ b/docs/downloads/top_results.xlsx
@@ -59,6 +59,27 @@
     <t xml:space="preserve">DHHS</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrated Viral Hepatitis Surveillance, Testing, Treatment, and Prevention Programs for Health Departments (IVH-STTP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCHHSTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forecasted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 139 days to deadline · about $7.5M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.5 FTE fits your staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/2e580529-c869-47d0-9aab-7d0e239ed5e8</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-007</t>
   </si>
   <si>
@@ -68,9 +89,6 @@
     <t xml:space="preserve">HHS-HRSA</t>
   </si>
   <si>
-    <t xml:space="preserve">forecasted</t>
-  </si>
-  <si>
     <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $22.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
@@ -80,22 +98,16 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/c30fddfd-2094-4cf0-ba21-04b6736fc755</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrated Viral Hepatitis Surveillance, Testing, Treatment, and Prevention Programs for Health Departments (IVH-STTP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-NCHHSTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 139 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.5 FTE fits your staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/2e580529-c869-47d0-9aab-7d0e239ed5e8</t>
+    <t xml:space="preserve">HRSA-27-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 Service Area Competition (SAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $19.2M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/51fa7e21-beca-497f-a0f1-bf175382f77f</t>
   </si>
   <si>
     <t xml:space="preserve">CDC-RFA-CK-27-0007</t>
@@ -113,18 +125,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/38e79010-c2a9-4d5f-bf81-cede591318e4</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year (FY) 2027 Service Area Competition (SAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $19.2M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/51fa7e21-beca-497f-a0f1-bf175382f77f</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-008</t>
   </si>
   <si>
@@ -146,6 +146,42 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/be465a8b-8694-4eef-9801-5160a92c7cdf</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controlling and Preventing STIs in US Health Departments (CAP-STIs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 103 days to deadline · about $8.5M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strengthening Services to Prevent the Infectious Disease Consequences of Drug Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 236 days to deadline · about $41.2M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIV Care Grant Program - Part B States/Territories Formula and AIDS Drug Assistance Program Formula and AIDS Drug Assistance Program Supplemental Awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · about $21.7M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1d55627c-531e-4a60-95e0-719b256179bf</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-077</t>
   </si>
   <si>
@@ -170,6 +206,45 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/d9551b09-3a45-4dc1-a343-3f09521de9aa</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 182 days to deadline · about $2.8M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 243 days to deadline · about $3.0M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 208 days to deadline · about $2.2M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
+  </si>
+  <si>
     <t xml:space="preserve">RFA-IP-27-035</t>
   </si>
   <si>
@@ -185,6 +260,21 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/b3577f33-eee0-49fb-aeba-2ea0b02fe59e</t>
   </si>
   <si>
+    <t xml:space="preserve">FOR-FD-23-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-FDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · no deadline stated · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-019</t>
   </si>
   <si>
@@ -221,18 +311,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/741f2935-18c1-4e3e-8f54-f30dc3a6ee80</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controlling and Preventing STIs in US Health Departments (CAP-STIs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 103 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-046</t>
   </si>
   <si>
@@ -245,58 +323,16 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/6bc69d9c-87b7-4329-962c-16c8e3ad553d</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 182 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 208 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 243 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR-FD-23-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-FDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · no deadline stated · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
+    <t xml:space="preserve">HRSA-27-079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 110 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-DP-27-051</t>
@@ -311,18 +347,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/54666d94-e0dc-44d3-90e6-6eb913f79ca9</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 110 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
-  </si>
-  <si>
     <t xml:space="preserve">RFA-OH-27-050</t>
   </si>
   <si>
@@ -359,18 +383,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8bb15754-c013-462d-b305-f2a8dd116e08</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strengthening Services to Prevent the Infectious Disease Consequences of Drug Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 236 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-039</t>
   </si>
   <si>
@@ -395,18 +407,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/18c0a9f1-fe39-4c7a-8ffd-1d8c656d666f</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIV Care Grant Program - Part B States/Territories Formula and AIDS Drug Assistance Program Formula and AIDS Drug Assistance Program Supplemental Awards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1d55627c-531e-4a60-95e0-719b256179bf</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDC-RFA-TP22-2201</t>
   </si>
   <si>
@@ -428,67 +428,151 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/42a1b238-2c19-47b4-ae58-f4a775231b78</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-DP-27-0043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statewide Perinatal Quality Collaboratives: Improving Perinatal Care and Outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 215 days to deadline · about $2.1M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-ACF-ORR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 366 days to deadline · up to $100.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-CK-26-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $6.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-OH-24-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Center for Construction Safety and Health Research and Translation (U54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · partner needed for research and rigorous evaluation · 62 days to deadline · up to $5.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b307f2ac-767d-4715-be92-f5326db2cd9d</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-DP-27-0072</t>
   </si>
   <si>
     <t xml:space="preserve">Promoting Population Health through Increased Capacity in Alcohol Epidemiology &amp; the Prevention of Excessive Alcohol Use</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 212 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 212 days to deadline · about $1.0M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/6d44bb23-2a1f-4e12-8d72-c2b5b46195d4</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-ACF-ORR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 366 days to deadline · up to $100.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-CK-26-035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $6.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-OH-24-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Center for Construction Safety and Health Research and Translation (U54)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · partner needed for research and rigorous evaluation · 62 days to deadline · up to $5.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b307f2ac-767d-4715-be92-f5326db2cd9d</t>
+    <t xml:space="preserve">HRSA-27-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing; partner needed for emergency management · 117 days to deadline · up to $4.9M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Needs emergency management, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-DP-27-036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 174 days to deadline · about $3.6M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 174 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $6.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 146 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
   </si>
   <si>
     <t xml:space="preserve">HRSA-27-042</t>
@@ -506,21 +590,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/02b2d236-f596-4aca-874d-b8e364156ddc</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing; partner needed for emergency management · 117 days to deadline · up to $4.9M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Needs emergency management, which DHHS reaches only through a partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDC-RFA-CE-27-0024</t>
   </si>
   <si>
@@ -539,46 +608,28 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/3c36bc50-73ae-42ad-a727-fae640dad5c9</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $6.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 174 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 146 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
+    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 244 days to deadline · about $2.8M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-OH-27-049</t>
@@ -593,16 +644,46 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/43e32c6d-fbbd-4056-8fd4-f64cdebefd41</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
+    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 159 days to deadline · about $1.4M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonstration Projects for Whole-Person Health Models for Women Living with HIV in the South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 166 days to deadline · about $2.5M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/06024144-a58a-42d8-8813-75357d9bb7fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-DHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 488 days to deadline · award not stated on Grants.gov · cost share required (25% stated) → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share required (25% stated): supervisor must approve match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-CK-26-036</t>
@@ -614,9 +695,6 @@
     <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
-    <t xml:space="preserve">Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/1a3231f6-36eb-40d1-afe8-232010fa2fe3</t>
   </si>
   <si>
@@ -632,72 +710,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/9accc70c-9683-4b78-bb7b-e8fdbcff1b47</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 159 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-DP-27-036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 174 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 244 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHS-DHS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 488 days to deadline · award not stated on Grants.gov · cost share required (25% stated) → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share required (25% stated): supervisor must approve match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DP-27-0043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statewide Perinatal Quality Collaboratives: Improving Perinatal Care and Outcomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 215 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
-  </si>
-  <si>
     <t xml:space="preserve">RFA-OH-25-003</t>
   </si>
   <si>
@@ -720,18 +732,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/f2ea8925-6244-47e8-8de5-ffe0007096e7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonstration Projects for Whole-Person Health Models for Women Living with HIV in the South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 166 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/06024144-a58a-42d8-8813-75357d9bb7fe</t>
   </si>
   <si>
     <t xml:space="preserve">VA-GPD-FORECAST-FY2026-FY2028</t>
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>14</v>
@@ -1279,10 +1279,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>46386</v>
+        <v>46434</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>22024900</v>
+        <v>7500000</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>18</v>
@@ -1320,9 +1320,11 @@
         <v>17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46434</v>
-      </c>
-      <c r="J3" s="3"/>
+        <v>46386</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>22024900</v>
+      </c>
       <c r="K3" s="3" t="s">
         <v>24</v>
       </c>
@@ -1353,25 +1355,25 @@
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>46386</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>19182000</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>46391</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -1385,25 +1387,25 @@
         <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>46386</v>
+        <v>46391</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>19182000</v>
+        <v>22000000</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>34</v>
@@ -1432,10 +1434,10 @@
         <v>36</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>17</v>
@@ -1450,7 +1452,7 @@
         <v>37</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>38</v>
@@ -1467,7 +1469,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>39</v>
@@ -1476,7 +1478,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -1491,7 +1493,7 @@
         <v>41</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>42</v>
@@ -1508,7 +1510,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>43</v>
@@ -1523,10 +1525,10 @@
         <v>17</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>46328</v>
+        <v>46398</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>10000000</v>
+        <v>8474576.27118644</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>45</v>
@@ -1549,7 +1551,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>47</v>
@@ -1564,16 +1566,16 @@
         <v>17</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>46407</v>
+        <v>46531</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>5149000</v>
+        <v>41250000</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>50</v>
@@ -1590,7 +1592,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>51</v>
@@ -1599,7 +1601,7 @@
         <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>17</v>
@@ -1608,16 +1610,16 @@
         <v>46387</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1140000</v>
+        <v>21716666.6666667</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -1631,34 +1633,34 @@
         <v>10</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>46328</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>46357</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -1672,13 +1674,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
@@ -1687,19 +1689,19 @@
         <v>17</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>46438</v>
+        <v>46407</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1000000</v>
+        <v>5149000</v>
       </c>
       <c r="K12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -1713,31 +1715,31 @@
         <v>12</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46497</v>
+        <v>46477</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1000000</v>
+        <v>2750000</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>66</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>67</v>
@@ -1754,7 +1756,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>68</v>
@@ -1763,20 +1765,22 @@
         <v>69</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>46398</v>
-      </c>
-      <c r="J14" s="3"/>
+        <v>46538</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>3000000</v>
+      </c>
       <c r="K14" s="3" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>71</v>
@@ -1793,7 +1797,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>72</v>
@@ -1802,16 +1806,16 @@
         <v>73</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>46464</v>
+        <v>46503</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>750000</v>
+        <v>2217391.30434783</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>74</v>
@@ -1834,7 +1838,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>76</v>
@@ -1849,14 +1853,16 @@
         <v>17</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>46477</v>
-      </c>
-      <c r="J16" s="3"/>
+        <v>46387</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>1140000</v>
+      </c>
       <c r="K16" s="3" t="s">
         <v>79</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>80</v>
@@ -1882,23 +1888,21 @@
         <v>82</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>46503</v>
-      </c>
+      <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -1912,13 +1916,13 @@
         <v>17</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
@@ -1927,17 +1931,19 @@
         <v>17</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>46538</v>
-      </c>
-      <c r="J18" s="3"/>
+        <v>46357</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="K18" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -1951,27 +1957,31 @@
         <v>18</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="I19" s="3" t="n">
+        <v>46438</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="K19" s="3" t="s">
         <v>92</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>93</v>
@@ -1988,7 +1998,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>94</v>
@@ -1997,22 +2007,22 @@
         <v>95</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46468</v>
+        <v>46497</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>725000</v>
+        <v>1000000</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>96</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>97</v>
@@ -2029,7 +2039,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>98</v>
@@ -2038,16 +2048,16 @@
         <v>99</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>46405</v>
+        <v>46464</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>700000</v>
+        <v>750000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>100</v>
@@ -2070,7 +2080,7 @@
         <v>21</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>102</v>
@@ -2079,22 +2089,22 @@
         <v>103</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>46386</v>
+        <v>46405</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>685000</v>
+        <v>700000</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>104</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>105</v>
@@ -2111,7 +2121,7 @@
         <v>22</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>106</v>
@@ -2120,22 +2130,22 @@
         <v>107</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46466</v>
+        <v>46468</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>650000</v>
+        <v>725000</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>108</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>109</v>
@@ -2152,7 +2162,7 @@
         <v>23</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>110</v>
@@ -2161,16 +2171,16 @@
         <v>111</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>46462</v>
+        <v>46386</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>500000</v>
+        <v>685000</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>112</v>
@@ -2208,14 +2218,16 @@
         <v>17</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>46531</v>
-      </c>
-      <c r="J25" s="3"/>
+        <v>46466</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>650000</v>
+      </c>
       <c r="K25" s="3" t="s">
         <v>116</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>117</v>
@@ -2232,7 +2244,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>118</v>
@@ -2241,13 +2253,13 @@
         <v>119</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46532</v>
+        <v>46462</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>500000</v>
@@ -2256,7 +2268,7 @@
         <v>120</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>121</v>
@@ -2273,7 +2285,7 @@
         <v>26</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>122</v>
@@ -2282,22 +2294,22 @@
         <v>123</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46508</v>
+        <v>46532</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>124</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>125</v>
@@ -2314,7 +2326,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>126</v>
@@ -2323,20 +2335,22 @@
         <v>127</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>46387</v>
-      </c>
-      <c r="J28" s="3"/>
+        <v>46508</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>300000</v>
+      </c>
       <c r="K28" s="3" t="s">
         <v>128</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>129</v>
@@ -2394,7 +2408,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>137</v>
@@ -2409,9 +2423,11 @@
         <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46507</v>
-      </c>
-      <c r="J30" s="3"/>
+        <v>46510</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>2141025.64102564</v>
+      </c>
       <c r="K30" s="3" t="s">
         <v>140</v>
       </c>
@@ -2483,7 +2499,7 @@
         <v>150</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>133</v>
@@ -2524,7 +2540,7 @@
         <v>155</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>133</v>
@@ -2565,25 +2581,25 @@
         <v>159</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>46483</v>
+        <v>46507</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>500000</v>
+        <v>1002916.66666667</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>160</v>
       </c>
       <c r="L34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M34" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="35">
@@ -2600,13 +2616,13 @@
         <v>58</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>17</v>
@@ -2618,13 +2634,13 @@
         <v>4900000</v>
       </c>
       <c r="K35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="M35" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="36">
@@ -2641,31 +2657,31 @@
         <v>58</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>3625000</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="L36" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>46494</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="K36" s="3" t="s">
+      <c r="M36" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="37">
@@ -2679,34 +2695,34 @@
         <v>9</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>46498</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>6750000</v>
-      </c>
-      <c r="K37" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="38">
@@ -2723,31 +2739,31 @@
         <v>57</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>46498</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="L38" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>46469</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="K38" s="3" t="s">
+      <c r="M38" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="39">
@@ -2764,13 +2780,13 @@
         <v>56</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>17</v>
@@ -2782,13 +2798,13 @@
         <v>5000000</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>141</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40">
@@ -2802,34 +2818,34 @@
         <v>12</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>46483</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="L40" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>46444</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="K40" s="3" t="s">
+      <c r="M40" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="41">
@@ -2843,34 +2859,34 @@
         <v>13</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>46498</v>
+        <v>46494</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>700000</v>
+        <v>1200000</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>194</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42">
@@ -2884,31 +2900,31 @@
         <v>14</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>46331</v>
+        <v>46539</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1000000</v>
+        <v>2750000</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>200</v>
@@ -2925,7 +2941,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>201</v>
@@ -2934,22 +2950,22 @@
         <v>202</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>46455</v>
+        <v>46498</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>900000</v>
+        <v>700000</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>203</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>204</v>
@@ -2966,7 +2982,7 @@
         <v>16</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>205</v>
@@ -2975,20 +2991,22 @@
         <v>206</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>46454</v>
-      </c>
-      <c r="J44" s="3"/>
+        <v>46444</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>1400000</v>
+      </c>
       <c r="K44" s="3" t="s">
         <v>207</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>208</v>
@@ -3005,7 +3023,7 @@
         <v>17</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>209</v>
@@ -3014,20 +3032,22 @@
         <v>210</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>46469</v>
-      </c>
-      <c r="J45" s="3"/>
+        <v>46454</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>1423076.92307692</v>
+      </c>
       <c r="K45" s="3" t="s">
         <v>211</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>212</v>
@@ -3044,7 +3064,7 @@
         <v>18</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>213</v>
@@ -3053,20 +3073,22 @@
         <v>214</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>46539</v>
-      </c>
-      <c r="J46" s="3"/>
+        <v>46461</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>2500000</v>
+      </c>
       <c r="K46" s="3" t="s">
         <v>215</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>216</v>
@@ -3122,7 +3144,7 @@
         <v>20</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>223</v>
@@ -3131,20 +3153,22 @@
         <v>224</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>46510</v>
-      </c>
-      <c r="J48" s="3"/>
+        <v>46331</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="K48" s="3" t="s">
         <v>225</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>226</v>
@@ -3161,7 +3185,7 @@
         <v>21</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>227</v>
@@ -3170,22 +3194,22 @@
         <v>228</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>47052</v>
+        <v>46455</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>550000</v>
+        <v>900000</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>229</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>230</v>
@@ -3202,7 +3226,7 @@
         <v>22</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>231</v>
@@ -3211,22 +3235,22 @@
         <v>232</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>46510</v>
+        <v>47052</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>233</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>234</v>
@@ -3243,7 +3267,7 @@
         <v>23</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>235</v>
@@ -3252,20 +3276,22 @@
         <v>236</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>46461</v>
-      </c>
-      <c r="J51" s="3"/>
+        <v>46510</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>450000</v>
+      </c>
       <c r="K51" s="3" t="s">
         <v>237</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>238</v>
@@ -3369,7 +3395,7 @@
         <v>252</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>17</v>

--- a/docs/downloads/top_results.xlsx
+++ b/docs/downloads/top_results.xlsx
@@ -6,7 +6,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="How to fill this in" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EXPLANATION" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Tier 1 - Writer can act" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Tier 2 - Supervisor" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Tier 3 - Secretary or legis." sheetId="4" state="visible" r:id="rId4"/>
@@ -18,45 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
-  <si>
-    <t xml:space="preserve">How to fill this in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One tab per tier. Each row is an opportunity in that tier in the tool's opening scenario (NC DHHS, plus NC DMVA's two Tier 3 items).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each rationale says why the opportunity ranks where it does and what the grant funds. Our five criteria:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deadline and award come from each opportunity's current record on Grants.gov (checked Sept 29-30, 2026). Forecast deadlines are Grants.gov's estimates. The award is Grants.gov's stated award ceiling; where it states none, the award is estimated as total program funding divided by the expected number of awards, and the Award source column says so. A blank award means Grants.gov gives neither.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact score (0-100) orders opportunities within a tier only; it never moves anything between tiers. For each of five parts the sheet shows the actual number and the points it adds; the points add up to the score (small differences are rounding).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Plan fit: the AI labeler's rating of fit with the agency's strategic plan. Strong earns full points, partial half, none zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  People reached: how many North Carolinians are in the population the opportunity serves (the population is named in the next column).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Help per person: the award per recipient divided by that population.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Award size: the award per recipient (shown in the Award per recipient column, with its source).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Program priorities: the writer's weight for the opportunity's program area, out of 3. The default is 1 for every area.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">People reached, help per person and award size earn points by how their number ranks against all the opportunities in the tool's view (about 400), not by the number alone. The biggest number gets full points; the median gets about half.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">With the default equal weights, each part can add at most 100 / (number of parts with a number): 20 points when all five have one. A blank part has no number, and the others share its points. People reached is blank when the population served has no NC count (people with a substance use disorder); help per person is blank when either the award or the people count is.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grants.gov ID is the number in grants.gov listing addresses; Simpler.Grants.gov ID is the code in the link, which opens the listing.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
+  <si>
+    <t xml:space="preserve">Our tool sorted grant opportunities into three tiers, instead of a singular list. These tiers are differentiated by the level of authority needed from a grant coordinator's perspective. Tier 1 grants can be directly acted upon by the grant writer using the tool. Tier 2 opportunities would need approval by a supervisor. Tier 3 grants, due to high matching costs or other factors, need oversight from upper legislature. The 3 tiers allow a user to make desicions about opportunities based on their capabilities and their priorities. Furthermore, within the tiers, the grants are sorted based on an "impact score" which is calculated with multiple metrics, including plan fit with the agency, people reached, population reached, help per person, and award size. While the weights for these metrics were equal, a user of our tool can adjust these weights according to their priorities. Also, there are a few opportunities chosen for the DMVA on this list, to showcase the generalizability of our model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How these results were ranked:</t>
   </si>
   <si>
     <t xml:space="preserve">Agency</t>
@@ -1166,7 +1133,7 @@
     <t xml:space="preserve">HHS-ACF</t>
   </si>
   <si>
-    <t xml:space="preserve">Top ranked in Tier 3 for strong plan fit and a large award (up to $15M), funding statewide early care and education data and technology infrastructure, but its 30% match and required state designation need the secretary.</t>
+    <t xml:space="preserve">Top ranked in Tier 3 for strong plan fit and a large award (up to $15M), funding statewide early care, education data and technology infrastructure, but its 30% match and required state designation need the secretary.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8d272419-96d1-4898-9706-0d86a1e63c03</t>
@@ -1205,7 +1172,7 @@
     <t xml:space="preserve">HHS-OPHS</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranked for a large award (up to $22M) and help per person, funding Title X family planning services statewide, with a required match that the data file missed and that likely needs an appropriation.</t>
+    <t xml:space="preserve">Ranked for a large award (up to $22M), help per person, and funding Title X family planning services statewide, with a required match that the data file missed and that likely needs an appropriation.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/770eae58-b245-4431-a4b8-7b1aca9e917f</t>
@@ -1232,7 +1199,7 @@
     <t xml:space="preserve">VA-CSHF</t>
   </si>
   <si>
-    <t xml:space="preserve">Top ranked for DMVA for strong plan fit and the highest help per veteran (about $444), funding construction and modernization of State Veterans Homes, which needs a 35% state match and an appropriation.</t>
+    <t xml:space="preserve">Top ranked for DMVA strong plan fit, the highest help per veteran (about $444), and funding construction and modernization of State Veterans Homes, but needs a 35% state match and an appropriation.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/59462b36-6d05-4832-a628-427f72260f3d</t>
@@ -1675,67 +1642,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1779,87 +1691,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -1868,7 +1780,7 @@
         <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E2" s="8" t="n">
         <v>20</v>
@@ -1877,7 +1789,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>13</v>
@@ -1892,7 +1804,7 @@
         <v>18.1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -1901,22 +1813,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46434</v>
@@ -1925,19 +1837,19 @@
         <v>7500000</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X2" s="5"/>
       <c r="Y2" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="Z2" s="9" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -1946,7 +1858,7 @@
         <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>10</v>
@@ -1955,7 +1867,7 @@
         <v>10584340</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>13</v>
@@ -1970,7 +1882,7 @@
         <v>19.6</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -1979,22 +1891,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46386</v>
@@ -2003,21 +1915,21 @@
         <v>22024900</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X3" s="5" t="n">
         <v>398400</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -2026,7 +1938,7 @@
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>10</v>
@@ -2035,7 +1947,7 @@
         <v>10584340</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>13</v>
@@ -2050,7 +1962,7 @@
         <v>19.2</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -2059,22 +1971,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46386</v>
@@ -2083,21 +1995,21 @@
         <v>19182000</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>1215700</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -2106,7 +2018,7 @@
         <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>10</v>
@@ -2115,7 +2027,7 @@
         <v>10584340</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>13</v>
@@ -2130,7 +2042,7 @@
         <v>19.5</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -2139,22 +2051,22 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>46391</v>
@@ -2163,21 +2075,21 @@
         <v>22000000</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>3500000</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -2186,7 +2098,7 @@
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>10</v>
@@ -2195,7 +2107,7 @@
         <v>10584340</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>13</v>
@@ -2210,7 +2122,7 @@
         <v>19.1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -2219,22 +2131,22 @@
         <v>6.7</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>46395</v>
@@ -2243,21 +2155,21 @@
         <v>15335500</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>567000</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
@@ -2266,7 +2178,7 @@
         <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>10</v>
@@ -2275,7 +2187,7 @@
         <v>10584340</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>13</v>
@@ -2290,7 +2202,7 @@
         <v>18.5</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -2299,22 +2211,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46461</v>
@@ -2323,19 +2235,19 @@
         <v>9000000</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X7" s="5"/>
       <c r="Y7" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="Z7" s="9" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -2344,7 +2256,7 @@
         <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>10</v>
@@ -2353,7 +2265,7 @@
         <v>10584340</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>13</v>
@@ -2368,7 +2280,7 @@
         <v>18.4</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>1</v>
@@ -2377,22 +2289,22 @@
         <v>6.7</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>46398</v>
@@ -2401,19 +2313,19 @@
         <v>8474576.27118644</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X8" s="5"/>
       <c r="Y8" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="Z8" s="9" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
@@ -2422,14 +2334,14 @@
         <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="7"/>
@@ -2438,7 +2350,7 @@
         <v>33</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
@@ -2447,22 +2359,22 @@
         <v>11.1</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>46531</v>
@@ -2471,19 +2383,19 @@
         <v>41250000</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X9" s="5"/>
       <c r="Y9" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
@@ -2492,7 +2404,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>10</v>
@@ -2501,7 +2413,7 @@
         <v>1073923</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>1.3</v>
@@ -2516,7 +2428,7 @@
         <v>19.3</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>1</v>
@@ -2525,22 +2437,22 @@
         <v>6.7</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>46387</v>
@@ -2549,19 +2461,19 @@
         <v>21716666.6666667</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X10" s="5"/>
       <c r="Y10" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="Z10" s="9" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -2570,7 +2482,7 @@
         <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>10</v>
@@ -2579,7 +2491,7 @@
         <v>1402172</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>2.7</v>
@@ -2594,7 +2506,7 @@
         <v>18.7</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>1</v>
@@ -2603,22 +2515,22 @@
         <v>6.7</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>46328</v>
@@ -2627,19 +2539,19 @@
         <v>10000000</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X11" s="5"/>
       <c r="Y11" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="Z11" s="9" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
@@ -2648,7 +2560,7 @@
         <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>10</v>
@@ -2657,7 +2569,7 @@
         <v>2322823</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>4.7</v>
@@ -2672,7 +2584,7 @@
         <v>17.6</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>1</v>
@@ -2681,22 +2593,22 @@
         <v>6.7</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>46407</v>
@@ -2705,21 +2617,21 @@
         <v>5149000</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>5149000</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="Z12" s="9" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
@@ -2728,7 +2640,7 @@
         <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>10</v>
@@ -2737,7 +2649,7 @@
         <v>10584340</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>13</v>
@@ -2752,7 +2664,7 @@
         <v>15.9</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>1</v>
@@ -2761,22 +2673,22 @@
         <v>6.7</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>46477</v>
@@ -2785,19 +2697,19 @@
         <v>2750000</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="Z13" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
@@ -2806,7 +2718,7 @@
         <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>10</v>
@@ -2815,7 +2727,7 @@
         <v>10584340</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>13</v>
@@ -2830,7 +2742,7 @@
         <v>16.2</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>1</v>
@@ -2839,22 +2751,22 @@
         <v>6.7</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>46538</v>
@@ -2863,19 +2775,19 @@
         <v>3000000</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X14" s="5"/>
       <c r="Y14" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="Z14" s="9" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
@@ -2884,7 +2796,7 @@
         <v>54</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>10</v>
@@ -2893,7 +2805,7 @@
         <v>10584340</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>13</v>
@@ -2908,7 +2820,7 @@
         <v>15.5</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>1</v>
@@ -2917,22 +2829,22 @@
         <v>6.7</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>46503</v>
@@ -2941,19 +2853,19 @@
         <v>2217391.30434783</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X15" s="5"/>
       <c r="Y15" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="Z15" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
@@ -2962,7 +2874,7 @@
         <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>10</v>
@@ -2971,7 +2883,7 @@
         <v>10584340</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>13</v>
@@ -2986,7 +2898,7 @@
         <v>12.7</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
@@ -2995,22 +2907,22 @@
         <v>6.7</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>46387</v>
@@ -3019,21 +2931,21 @@
         <v>1140000</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>850000</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="Z16" s="9" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
@@ -3042,7 +2954,7 @@
         <v>49</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>16.7</v>
@@ -3051,7 +2963,7 @@
         <v>10584340</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>21.7</v>
@@ -3060,7 +2972,7 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
@@ -3069,39 +2981,39 @@
         <v>11.1</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="5"/>
       <c r="W17" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="X17" s="5"/>
       <c r="Y17" s="2" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="Z17" s="9" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
@@ -3110,7 +3022,7 @@
         <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>10</v>
@@ -3119,7 +3031,7 @@
         <v>10584340</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>13</v>
@@ -3134,7 +3046,7 @@
         <v>11.9</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
@@ -3143,22 +3055,22 @@
         <v>6.7</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>46357</v>
@@ -3167,21 +3079,21 @@
         <v>1000000</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X18" s="5" t="n">
         <v>1000000</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="Z18" s="9" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
@@ -3190,7 +3102,7 @@
         <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>10</v>
@@ -3199,7 +3111,7 @@
         <v>10584340</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>13</v>
@@ -3214,7 +3126,7 @@
         <v>11.9</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>1</v>
@@ -3223,22 +3135,22 @@
         <v>6.7</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>46438</v>
@@ -3247,21 +3159,21 @@
         <v>1000000</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X19" s="5" t="n">
         <v>350000</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="Z19" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
@@ -3270,7 +3182,7 @@
         <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>10</v>
@@ -3279,7 +3191,7 @@
         <v>127227</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>0.3</v>
@@ -3294,7 +3206,7 @@
         <v>11.9</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -3303,22 +3215,22 @@
         <v>6.7</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>46497</v>
@@ -3327,19 +3239,19 @@
         <v>1000000</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X20" s="5"/>
       <c r="Y20" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="Z20" s="9" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
@@ -3348,7 +3260,7 @@
         <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>10</v>
@@ -3357,7 +3269,7 @@
         <v>10584340</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>13</v>
@@ -3372,7 +3284,7 @@
         <v>10.6</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>1</v>
@@ -3381,22 +3293,22 @@
         <v>6.7</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>46464</v>
@@ -3405,19 +3317,19 @@
         <v>750000</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X21" s="5"/>
       <c r="Y21" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="Z21" s="9" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
@@ -3426,7 +3338,7 @@
         <v>44</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>10</v>
@@ -3435,7 +3347,7 @@
         <v>10584340</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>13</v>
@@ -3450,7 +3362,7 @@
         <v>9.6</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -3459,22 +3371,22 @@
         <v>6.7</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>46405</v>
@@ -3483,19 +3395,19 @@
         <v>700000</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X22" s="5"/>
       <c r="Y22" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="Z22" s="9" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
@@ -3504,7 +3416,7 @@
         <v>44</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>10</v>
@@ -3513,7 +3425,7 @@
         <v>10584340</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>13</v>
@@ -3528,7 +3440,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -3537,22 +3449,22 @@
         <v>6.7</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>46468</v>
@@ -3561,21 +3473,21 @@
         <v>725000</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X23" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="Z23" s="9" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
@@ -3584,7 +3496,7 @@
         <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>10</v>
@@ -3593,7 +3505,7 @@
         <v>10584340</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>13</v>
@@ -3608,7 +3520,7 @@
         <v>9.4</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
@@ -3617,22 +3529,22 @@
         <v>6.7</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>46386</v>
@@ -3641,21 +3553,21 @@
         <v>685000</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X24" s="5" t="n">
         <v>150000</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="Z24" s="9" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -3664,7 +3576,7 @@
         <v>42</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>10</v>
@@ -3673,7 +3585,7 @@
         <v>10584340</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>13</v>
@@ -3688,7 +3600,7 @@
         <v>9.2</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
@@ -3697,22 +3609,22 @@
         <v>6.7</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U25" s="4" t="n">
         <v>46466</v>
@@ -3721,19 +3633,19 @@
         <v>650000</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X25" s="5"/>
       <c r="Y25" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="Z25" s="9" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>25</v>
@@ -3742,7 +3654,7 @@
         <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>10</v>
@@ -3751,7 +3663,7 @@
         <v>10584340</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>13</v>
@@ -3766,7 +3678,7 @@
         <v>6.9</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>1</v>
@@ -3775,22 +3687,22 @@
         <v>6.7</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>46462</v>
@@ -3799,21 +3711,21 @@
         <v>500000</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X26" s="5" t="n">
         <v>300000</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="Z26" s="9" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>26</v>
@@ -3822,7 +3734,7 @@
         <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>10</v>
@@ -3831,7 +3743,7 @@
         <v>10584340</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>13</v>
@@ -3846,7 +3758,7 @@
         <v>6.9</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>1</v>
@@ -3855,22 +3767,22 @@
         <v>6.7</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U27" s="4" t="n">
         <v>46532</v>
@@ -3879,21 +3791,21 @@
         <v>500000</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X27" s="5" t="n">
         <v>250000</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="Z27" s="9" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>27</v>
@@ -3902,7 +3814,7 @@
         <v>35</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>10</v>
@@ -3911,7 +3823,7 @@
         <v>10584340</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>13</v>
@@ -3926,7 +3838,7 @@
         <v>3.9</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>1</v>
@@ -3935,22 +3847,22 @@
         <v>6.7</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>46508</v>
@@ -3959,14 +3871,14 @@
         <v>300000</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X28" s="5"/>
       <c r="Y28" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="Z28" s="9" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -4040,87 +3952,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -4129,7 +4041,7 @@
         <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E2" s="12" t="n">
         <v>20</v>
@@ -4138,7 +4050,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>13</v>
@@ -4153,7 +4065,7 @@
         <v>17.3</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -4162,22 +4074,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46429</v>
@@ -4186,21 +4098,21 @@
         <v>5000000</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>50000</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="Z2" s="9" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -4209,7 +4121,7 @@
         <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>20</v>
@@ -4218,7 +4130,7 @@
         <v>127227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H3" s="12" t="n">
         <v>0.3</v>
@@ -4233,7 +4145,7 @@
         <v>15.3</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -4242,22 +4154,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46510</v>
@@ -4266,19 +4178,19 @@
         <v>2141025.64102564</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X3" s="5"/>
       <c r="Y3" s="2" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -4287,7 +4199,7 @@
         <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>10</v>
@@ -4296,7 +4208,7 @@
         <v>2322823</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>4.7</v>
@@ -4311,7 +4223,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -4320,22 +4232,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46661</v>
@@ -4344,21 +4256,21 @@
         <v>100000000</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>1000000</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -4367,7 +4279,7 @@
         <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>10</v>
@@ -4376,7 +4288,7 @@
         <v>10584340</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>13</v>
@@ -4391,7 +4303,7 @@
         <v>17.8</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -4400,22 +4312,22 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>46331</v>
@@ -4424,21 +4336,21 @@
         <v>6000000</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>1750000</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -4447,7 +4359,7 @@
         <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>10</v>
@@ -4456,7 +4368,7 @@
         <v>10584340</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>13</v>
@@ -4471,7 +4383,7 @@
         <v>17.7</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -4480,22 +4392,22 @@
         <v>6.7</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>46357</v>
@@ -4504,21 +4416,21 @@
         <v>5750000</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>3000000</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
@@ -4527,7 +4439,7 @@
         <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>20</v>
@@ -4536,7 +4448,7 @@
         <v>10584340</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>13</v>
@@ -4551,7 +4463,7 @@
         <v>12.4</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -4560,22 +4472,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46507</v>
@@ -4584,19 +4496,19 @@
         <v>1002916.66666667</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X7" s="5"/>
       <c r="Y7" s="2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="Z7" s="9" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -4605,7 +4517,7 @@
         <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>10</v>
@@ -4614,7 +4526,7 @@
         <v>10584340</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>13</v>
@@ -4629,7 +4541,7 @@
         <v>17.1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>1</v>
@@ -4638,22 +4550,22 @@
         <v>6.7</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>46412</v>
@@ -4662,21 +4574,21 @@
         <v>4900000</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>790000</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="Z8" s="9" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
@@ -4685,7 +4597,7 @@
         <v>58</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>10</v>
@@ -4694,7 +4606,7 @@
         <v>10584340</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>13</v>
@@ -4709,7 +4621,7 @@
         <v>16.8</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
@@ -4718,22 +4630,22 @@
         <v>6.7</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>46469</v>
@@ -4742,19 +4654,19 @@
         <v>3625000</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X9" s="5"/>
       <c r="Y9" s="2" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
@@ -4763,14 +4675,14 @@
         <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="11"/>
@@ -4779,7 +4691,7 @@
         <v>28.9</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>1</v>
@@ -4788,22 +4700,22 @@
         <v>11.1</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>46469</v>
@@ -4812,21 +4724,21 @@
         <v>5000000</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X10" s="5" t="n">
         <v>5000000</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="Z10" s="9" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -4835,7 +4747,7 @@
         <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>10</v>
@@ -4844,7 +4756,7 @@
         <v>2322823</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>4.7</v>
@@ -4859,7 +4771,7 @@
         <v>18</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>1</v>
@@ -4868,22 +4780,22 @@
         <v>6.7</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>46498</v>
@@ -4892,21 +4804,21 @@
         <v>6750000</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X11" s="5" t="n">
         <v>6750000</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="Z11" s="9" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
@@ -4915,7 +4827,7 @@
         <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>10</v>
@@ -4924,7 +4836,7 @@
         <v>2322823</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>4.7</v>
@@ -4939,7 +4851,7 @@
         <v>17.3</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>1</v>
@@ -4948,22 +4860,22 @@
         <v>6.7</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>46441</v>
@@ -4972,21 +4884,21 @@
         <v>5000000</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>5000000</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="Z12" s="9" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
@@ -4995,14 +4907,14 @@
         <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>33.3</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="11"/>
@@ -5011,7 +4923,7 @@
         <v>11.6</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>1</v>
@@ -5020,22 +4932,22 @@
         <v>11.1</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>46483</v>
@@ -5044,19 +4956,19 @@
         <v>500000</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="2" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="Z13" s="9" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
@@ -5065,7 +4977,7 @@
         <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>20</v>
@@ -5074,7 +4986,7 @@
         <v>1402172</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>2.7</v>
@@ -5089,7 +5001,7 @@
         <v>13</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>1</v>
@@ -5098,22 +5010,22 @@
         <v>6.7</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>46494</v>
@@ -5122,21 +5034,21 @@
         <v>1200000</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>650000</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="Z14" s="9" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
@@ -5145,7 +5057,7 @@
         <v>56</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>10</v>
@@ -5154,7 +5066,7 @@
         <v>10584340</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>13</v>
@@ -5169,7 +5081,7 @@
         <v>15.9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>1</v>
@@ -5178,22 +5090,22 @@
         <v>6.7</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>46539</v>
@@ -5202,19 +5114,19 @@
         <v>2750000</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X15" s="5"/>
       <c r="Y15" s="2" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="Z15" s="9" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
@@ -5223,7 +5135,7 @@
         <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>20</v>
@@ -5232,7 +5144,7 @@
         <v>2322823</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>4.7</v>
@@ -5247,7 +5159,7 @@
         <v>9.6</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
@@ -5256,22 +5168,22 @@
         <v>6.7</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>46498</v>
@@ -5280,21 +5192,21 @@
         <v>700000</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>700000</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="Z16" s="9" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
@@ -5303,7 +5215,7 @@
         <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>10</v>
@@ -5312,7 +5224,7 @@
         <v>10584340</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>13</v>
@@ -5327,7 +5239,7 @@
         <v>13.4</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
@@ -5336,22 +5248,22 @@
         <v>6.7</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>46444</v>
@@ -5360,21 +5272,21 @@
         <v>1400000</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X17" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="Z17" s="9" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
@@ -5383,7 +5295,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>10</v>
@@ -5392,7 +5304,7 @@
         <v>10584340</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>13</v>
@@ -5407,7 +5319,7 @@
         <v>13.5</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
@@ -5416,22 +5328,22 @@
         <v>6.7</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>46454</v>
@@ -5440,19 +5352,19 @@
         <v>1423076.92307692</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X18" s="5"/>
       <c r="Y18" s="2" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="Z18" s="9" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
@@ -5461,7 +5373,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>10</v>
@@ -5470,7 +5382,7 @@
         <v>1402172</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>2.7</v>
@@ -5485,7 +5397,7 @@
         <v>15.7</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>1</v>
@@ -5494,22 +5406,22 @@
         <v>6.7</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>46461</v>
@@ -5518,19 +5430,19 @@
         <v>2500000</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X19" s="5"/>
       <c r="Y19" s="2" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="Z19" s="9" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
@@ -5539,7 +5451,7 @@
         <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>16.7</v>
@@ -5548,7 +5460,7 @@
         <v>10584340</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>21.7</v>
@@ -5557,7 +5469,7 @@
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
       <c r="L20" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -5566,41 +5478,41 @@
         <v>11.1</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>46783</v>
       </c>
       <c r="V20" s="5"/>
       <c r="W20" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="X20" s="5"/>
       <c r="Y20" s="2" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="Z20" s="9" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
@@ -5609,7 +5521,7 @@
         <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>10</v>
@@ -5618,7 +5530,7 @@
         <v>10584340</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>13</v>
@@ -5633,7 +5545,7 @@
         <v>11.9</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>1</v>
@@ -5642,22 +5554,22 @@
         <v>6.7</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>46331</v>
@@ -5666,21 +5578,21 @@
         <v>1000000</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X21" s="5" t="n">
         <v>750000</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="Z21" s="9" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
@@ -5689,7 +5601,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>10</v>
@@ -5698,7 +5610,7 @@
         <v>10584340</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>13</v>
@@ -5713,7 +5625,7 @@
         <v>11.3</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -5722,22 +5634,22 @@
         <v>6.7</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>46455</v>
@@ -5746,21 +5658,21 @@
         <v>900000</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X22" s="5" t="n">
         <v>450000</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="Z22" s="9" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
@@ -5769,7 +5681,7 @@
         <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>10</v>
@@ -5778,7 +5690,7 @@
         <v>10584340</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>13</v>
@@ -5793,7 +5705,7 @@
         <v>8.4</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -5802,22 +5714,22 @@
         <v>6.7</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>47052</v>
@@ -5826,21 +5738,21 @@
         <v>550000</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X23" s="5" t="n">
         <v>50000</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="Z23" s="9" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
@@ -5849,7 +5761,7 @@
         <v>37</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>10</v>
@@ -5858,7 +5770,7 @@
         <v>10584340</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>13</v>
@@ -5873,7 +5785,7 @@
         <v>5.3</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
@@ -5882,22 +5794,22 @@
         <v>6.7</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>46510</v>
@@ -5906,21 +5818,21 @@
         <v>450000</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X24" s="5" t="n">
         <v>450000</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="Z24" s="9" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -5929,7 +5841,7 @@
         <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>16.7</v>
@@ -5938,7 +5850,7 @@
         <v>618846</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>1.7</v>
@@ -5947,7 +5859,7 @@
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
       <c r="L25" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
@@ -5956,34 +5868,34 @@
         <v>11.1</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="5"/>
       <c r="W25" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="X25" s="5"/>
       <c r="Y25" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="Z25" s="9" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -6054,87 +5966,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -6143,7 +6055,7 @@
         <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E2" s="15" t="n">
         <v>20</v>
@@ -6152,7 +6064,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H2" s="15" t="n">
         <v>13</v>
@@ -6167,7 +6079,7 @@
         <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -6176,22 +6088,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46346</v>
@@ -6200,21 +6112,21 @@
         <v>15000000</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="Z2" s="9" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -6223,7 +6135,7 @@
         <v>67</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E3" s="15" t="n">
         <v>20</v>
@@ -6232,7 +6144,7 @@
         <v>127227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H3" s="15" t="n">
         <v>0.3</v>
@@ -6247,7 +6159,7 @@
         <v>19.9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -6256,22 +6168,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46464</v>
@@ -6280,21 +6192,21 @@
         <v>48596938</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X3" s="5" t="n">
         <v>3285203</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -6303,7 +6215,7 @@
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>10</v>
@@ -6312,7 +6224,7 @@
         <v>10584340</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>13</v>
@@ -6327,7 +6239,7 @@
         <v>19.5</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -6336,22 +6248,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46398</v>
@@ -6360,21 +6272,21 @@
         <v>22000000</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>200000</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -6383,7 +6295,7 @@
         <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>20</v>
@@ -6392,7 +6304,7 @@
         <v>618846</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>10</v>
@@ -6407,7 +6319,7 @@
         <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -6416,43 +6328,43 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="5" t="n">
         <v>275000000</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>260000</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -6461,7 +6373,7 @@
         <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E6" s="15" t="n">
         <v>33.3</v>
@@ -6470,7 +6382,7 @@
         <v>618846</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>16.7</v>
@@ -6479,7 +6391,7 @@
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
       <c r="L6" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -6488,39 +6400,39 @@
         <v>11.1</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="5"/>
       <c r="W6" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="X6" s="5"/>
       <c r="Y6" s="2" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
@@ -6529,7 +6441,7 @@
         <v>37</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>20</v>
@@ -6538,7 +6450,7 @@
         <v>618846</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>10</v>
@@ -6553,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -6562,22 +6474,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46486</v>
@@ -6586,16 +6498,16 @@
         <v>400000</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>50000</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="Z7" s="9" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/top_results.xlsx
+++ b/docs/downloads/top_results.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
   <si>
-    <t xml:space="preserve">Our tool sorted grant opportunities into three tiers, instead of a singular list. These tiers are differentiated by the level of authority needed from a grant coordinator's perspective. Tier 1 grants can be directly acted upon by the grant writer using the tool. Tier 2 opportunities would need approval by a supervisor. Tier 3 grants, due to high matching costs or other factors, need oversight from upper legislature. The 3 tiers allow a user to make desicions about opportunities based on their capabilities and their priorities. Furthermore, within the tiers, the grants are sorted based on an "impact score" which is calculated with multiple metrics, including plan fit with the agency, people reached, population reached, help per person, and award size. While the weights for these metrics were equal, a user of our tool can adjust these weights according to their priorities. Also, there are a few opportunities chosen for the DMVA on this list, to showcase the generalizability of our model.</t>
+    <t xml:space="preserve">Our tool sorted grant opportunities into three tiers, instead of a singular list. These tiers are differentiated by the level of authority needed from a grant coordinator's perspective. Tier 1 grants can be directly acted upon by the grant writer using the tool. Tier 2 opportunities would need approval by a supervisor. Tier 3 grants, due to high matching costs or other factors, need approval from the secretary or the legislature. The 3 tiers allow a user to make decisions about opportunities based on their capabilities and their priorities. Furthermore, within the tiers, the grants are sorted based on an "impact score" which is calculated with multiple metrics, including plan fit with the agency's strategic plan, people reached, help per person, award size, and program priorities. While the weights for these metrics were equal, a user of our tool can adjust these weights according to their priorities. Also, there are a few opportunities chosen for the DMVA on this list, to showcase the generalizability of our model.</t>
   </si>
   <si>
     <t xml:space="preserve">How these results were ranked:</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">HHS-ACF</t>
   </si>
   <si>
-    <t xml:space="preserve">Top ranked in Tier 3 for strong plan fit and a large award (up to $15M), funding statewide early care, education data and technology infrastructure, but its 30% match and required state designation need the secretary.</t>
+    <t xml:space="preserve">Top ranked in Tier 3 for strong plan fit and a large award (up to $15M), funding statewide early care and education data and technology infrastructure, but its 30% match and required state designation need the secretary.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8d272419-96d1-4898-9706-0d86a1e63c03</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">VA-CSHF</t>
   </si>
   <si>
-    <t xml:space="preserve">Top ranked for DMVA strong plan fit, the highest help per veteran (about $444), and funding construction and modernization of State Veterans Homes, but needs a 35% state match and an appropriation.</t>
+    <t xml:space="preserve">Top ranked for DMVA for strong plan fit, the highest help per veteran (about $444), and funding construction and modernization of State Veterans Homes, but needs a 35% state match and an appropriation.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/59462b36-6d05-4832-a628-427f72260f3d</t>
